--- a/HR Analytics Dashboard.xlsx
+++ b/HR Analytics Dashboard.xlsx
@@ -4,20 +4,22 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="hr_analytics_500_rows" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Top 5 Emp" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="COUNT of Employee_ID" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="COUNTA of Name vs Location" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Year Hiring Trend" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="Pivot Table 5" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="Dashboard" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="Pivot Table 2" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="Pivot Table 17" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Top 5 Emp" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="COUNT of Employee_ID" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="COUNTA of Name vs Location" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Year Hiring Trend" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="Pivot Table 5" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="Dashboard" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="Pivot Table 2" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="Detail2-Marketing" sheetId="10" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">'COUNTA of Name vs Location'!$A$1:$B$102</definedName>
-    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">'Pivot Table 5'!$A$1:$B$7</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_3B717D27_9F4F_4753_8CC6_37024164C384_.wvu.FilterData">hr_analytics_500_rows!$A$1:$O$501</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_3B717D27_9F4F_4753_8CC6_37024164C384_.wvu.FilterData">hr_analytics_500_rows!$A$1:$O$501</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_3B717D27_9F4F_4753_8CC6_37024164C384_.wvu.FilterData">hr_analytics_500_rows!$A$1:$O$501</definedName>
+    <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">'COUNTA of Name vs Location'!$A$1:$B$102</definedName>
+    <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">'Pivot Table 5'!$A$1:$B$7</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_EB8B8BF7_1C38_44E1_877B_F903761F8CA0_.wvu.FilterData">hr_analytics_500_rows!$A$1:$O$501</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_EB8B8BF7_1C38_44E1_877B_F903761F8CA0_.wvu.FilterData">hr_analytics_500_rows!$A$1:$O$501</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_EB8B8BF7_1C38_44E1_877B_F903761F8CA0_.wvu.FilterData">hr_analytics_500_rows!$A$1:$O$501</definedName>
     <definedName name="SlicerCache_Table_1_Col_4">#N/A</definedName>
     <definedName name="SlicerCache_Table_1_Col_5">#N/A</definedName>
     <definedName name="SlicerCache_Table_1_Col_9">#N/A</definedName>
@@ -25,19 +27,19 @@
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{3B717D27-9F4F-4753-8CC6-37024164C384}" name="Filter 1"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{EB8B8BF7-1C38-44E1-877B-F903761F8CA0}" name="Filter 1"/>
   </customWorkbookViews>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId13"/>
-    <pivotCache cacheId="1" r:id="rId14"/>
+    <pivotCache cacheId="0" r:id="rId15"/>
+    <pivotCache cacheId="1" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
       <x15:slicerCaches>
-        <x14:slicerCache r:id="rId15"/>
-        <x14:slicerCache r:id="rId16"/>
         <x14:slicerCache r:id="rId17"/>
         <x14:slicerCache r:id="rId18"/>
+        <x14:slicerCache r:id="rId19"/>
+        <x14:slicerCache r:id="rId20"/>
       </x15:slicerCaches>
     </ext>
   </extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4074" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4641" uniqueCount="146">
   <si>
     <t>Employee_ID</t>
   </si>
@@ -464,6 +466,9 @@
     <t>Anika Sharma</t>
   </si>
   <si>
+    <t>COUNTA of Department</t>
+  </si>
+  <si>
     <t>COUNT of Employee_ID</t>
   </si>
   <si>
@@ -489,7 +494,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -516,6 +521,12 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -537,13 +548,76 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border/>
+    <border>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFA3B2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFA3B2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="FFA3B2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA3B2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA3B2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA3B2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA3B2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <top style="thin">
+        <color rgb="FFA3B2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA3B2CC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -568,11 +642,29 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
     <dxf>
       <font/>
       <fill>
@@ -580,680 +672,48 @@
       </fill>
       <border/>
     </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6C7687"/>
+          <bgColor rgb="FF6C7687"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEBEFF1"/>
+          <bgColor rgb="FFEBEFF1"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
   </dxfs>
+  <tableStyles count="1">
+    <tableStyle count="3" pivot="0" name="Detail2-Marketing-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-  <c:chart>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Top 5 Emp'!$E$4:$E$8</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Top 5 Emp'!$F$4:$F$8</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:axId val="2023362698"/>
-        <c:axId val="592554873"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="2023362698"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:spPr/>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="592554873"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="592554873"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2023362698"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr b="0">
-              <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>TOP 5 Employee</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Top 5 Emp'!$E$4:$E$8</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Top 5 Emp'!$F$4:$F$8</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:axId val="1707151030"/>
-        <c:axId val="771568634"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1707151030"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:spPr/>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="771568634"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="771568634"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1707151030"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr b="0">
-              <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="1" sz="1400">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1" sz="1400">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>AVERAGE of Salary of Job_Role</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:view3D>
-      <c:rotX val="15"/>
-      <c:rotY val="20"/>
-      <c:depthPercent val="100"/>
-      <c:rAngAx val="1"/>
-    </c:view3D>
-    <c:plotArea>
-      <c:layout/>
-      <c:bar3DChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Pivot Table 5'!$B$1</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:dPt>
-            <c:idx val="0"/>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pivot Table 5'!$A$2:$A$7</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Pivot Table 5'!$B$2:$B$7</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:axId val="2039094058"/>
-        <c:axId val="583178411"/>
-      </c:bar3DChart>
-      <c:catAx>
-        <c:axId val="2039094058"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>Job_Role</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:spPr/>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="583178411"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="583178411"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>AVERAGE of Salary</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2039094058"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr b="1">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
   <c:chart>
     <c:title>
@@ -1277,7 +737,7 @@
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>COUNT of Employee_ID vs Department</a:t>
+              <a:t>COUNTA of Department vs Department</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1293,7 +753,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Pivot Table 2'!$B$1</c:f>
+              <c:f>'Pivot Table 17'!$B$1</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1308,21 +768,21 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot Table 2'!$A$2:$A$8</c:f>
+              <c:f>'Pivot Table 17'!$A$2:$A$8</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot Table 2'!$B$2:$B$8</c:f>
+              <c:f>'Pivot Table 17'!$B$2:$B$8</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="2107698993"/>
-        <c:axId val="2033677075"/>
+        <c:axId val="569510832"/>
+        <c:axId val="546082862"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2107698993"/>
+        <c:axId val="569510832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1374,10 +834,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2033677075"/>
+        <c:crossAx val="546082862"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2033677075"/>
+        <c:axId val="546082862"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1424,7 +884,7 @@
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                   </a:rPr>
-                  <a:t>COUNT of Employee_ID</a:t>
+                  <a:t>COUNTA of Department</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1452,7 +912,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2107698993"/>
+        <c:crossAx val="569510832"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1478,481 +938,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-  <c:chart>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'COUNT of Employee_ID'!$B$1:$B$2</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:cat>
-            <c:strRef>
-              <c:f>'COUNT of Employee_ID'!$A$3:$A$9</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'COUNT of Employee_ID'!$B$3:$B$9</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'COUNT of Employee_ID'!$C$1:$C$2</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:cat>
-            <c:strRef>
-              <c:f>'COUNT of Employee_ID'!$A$3:$A$9</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'COUNT of Employee_ID'!$C$3:$C$9</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'COUNT of Employee_ID'!$D$1:$D$2</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'COUNT of Employee_ID'!$A$3:$A$9</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'COUNT of Employee_ID'!$D$3:$D$9</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:overlap val="100"/>
-        <c:axId val="1339134957"/>
-        <c:axId val="1912159287"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1339134957"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:spPr/>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1912159287"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1912159287"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1339134957"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr b="0">
-              <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>COUNTA of Name vs Location</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'COUNTA of Name vs Location'!$B$1</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:cat>
-            <c:strRef>
-              <c:f>'COUNTA of Name vs Location'!$A$2:$A$7</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'COUNTA of Name vs Location'!$B$2:$B$7</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:axId val="1618350362"/>
-        <c:axId val="1704198028"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1618350362"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>Location</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:spPr/>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1704198028"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1704198028"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>COUNTA of Name</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1618350362"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr b="0">
-              <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
   <c:chart>
     <c:title>
@@ -2172,11 +1158,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="2117434316"/>
-        <c:axId val="365666539"/>
+        <c:axId val="1385742149"/>
+        <c:axId val="834629997"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2117434316"/>
+        <c:axId val="1385742149"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2228,10 +1214,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="365666539"/>
+        <c:crossAx val="834629997"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="365666539"/>
+        <c:axId val="834629997"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2306,7 +1292,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2117434316"/>
+        <c:crossAx val="1385742149"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2332,7 +1318,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
   <c:chart>
     <c:title>
@@ -2356,7 +1342,7 @@
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>AVERAGE of Salary of Job_Role</a:t>
+              <a:t>TOP 5 Employee</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2367,15 +1353,9 @@
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Pivot Table 5'!$B$1</c:f>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -2386,9 +1366,6 @@
               </a:solidFill>
             </a:ln>
           </c:spPr>
-          <c:dPt>
-            <c:idx val="0"/>
-          </c:dPt>
           <c:dLbls>
             <c:numFmt formatCode="General" sourceLinked="1"/>
             <c:txPr>
@@ -2413,600 +1390,21 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot Table 5'!$A$2:$A$7</c:f>
+              <c:f>'Top 5 Emp'!$E$4:$E$8</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot Table 5'!$B$2:$B$7</c:f>
+              <c:f>'Top 5 Emp'!$F$4:$F$8</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:overlap val="100"/>
-        <c:axId val="76351416"/>
-        <c:axId val="1319565570"/>
+        <c:axId val="1665597092"/>
+        <c:axId val="2013987034"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="76351416"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>Job_Role</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:spPr/>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1319565570"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1319565570"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>AVERAGE of Salary</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="76351416"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr b="0">
-              <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Salary vs Experience_Years</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>hr_analytics_500_rows!$H$1</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln cmpd="sng">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>hr_analytics_500_rows!$G$2:$G$1000</c:f>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>hr_analytics_500_rows!$H$2:$H$1000</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:yVal>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="501657058"/>
-        <c:axId val="1553279597"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="501657058"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>Experience_Years</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1553279597"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1553279597"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>Salary</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="501657058"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr b="0">
-              <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Department-wise Attrition Rate </a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'COUNT of Employee_ID'!$B$1:$B$2</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr>
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'COUNT of Employee_ID'!$A$3:$A$9</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'COUNT of Employee_ID'!$B$3:$B$9</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'COUNT of Employee_ID'!$C$1:$C$2</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr>
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'COUNT of Employee_ID'!$A$3:$A$9</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'COUNT of Employee_ID'!$C$3:$C$9</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'COUNT of Employee_ID'!$D$1:$D$2</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'COUNT of Employee_ID'!$A$3:$A$9</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'COUNT of Employee_ID'!$D$3:$D$9</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:overlap val="100"/>
-        <c:axId val="674327505"/>
-        <c:axId val="1140328598"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="674327505"/>
+        <c:axId val="1665597092"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3058,15 +1456,24 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1140328598"/>
+        <c:crossAx val="2013987034"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1140328598"/>
+        <c:axId val="2013987034"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:minorGridlines>
           <c:spPr>
             <a:ln>
@@ -3118,7 +1525,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="1" sz="1000">
+              <a:defRPr b="1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3127,7 +1534,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="674327505"/>
+        <c:crossAx val="1665597092"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -3138,7 +1545,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr lvl="0">
-            <a:defRPr b="1">
+            <a:defRPr b="0">
               <a:solidFill>
                 <a:srgbClr val="1A1A1A"/>
               </a:solidFill>
@@ -3153,7 +1560,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
   <c:chart>
     <c:title>
@@ -3177,7 +1584,7 @@
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>Location-wise Employees</a:t>
+              <a:t> Department wise Employees</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3193,7 +1600,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'COUNTA of Name vs Location'!$B$1</c:f>
+              <c:f>'Pivot Table 17'!$B$1</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -3230,6 +1637,897 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
+              <c:f>'Pivot Table 17'!$A$2:$A$8</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pivot Table 17'!$B$2:$B$8</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1255454320"/>
+        <c:axId val="836107159"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1255454320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Department</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="836107159"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="836107159"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>COUNTA of Department</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1255454320"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>COUNT of Employee_ID vs Department</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Pivot Table 2'!$B$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pivot Table 2'!$A$2:$A$8</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pivot Table 2'!$B$2:$B$8</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1574952044"/>
+        <c:axId val="1890802731"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1574952044"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Department</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1890802731"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1890802731"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>COUNT of Employee_ID</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1574952044"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Top 5 Emp'!$E$4:$E$8</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Top 5 Emp'!$F$4:$F$8</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1640621453"/>
+        <c:axId val="1398620342"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1640621453"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1398620342"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1398620342"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1640621453"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'COUNT of Employee_ID'!$B$1:$B$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'COUNT of Employee_ID'!$A$3:$A$9</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'COUNT of Employee_ID'!$B$3:$B$9</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'COUNT of Employee_ID'!$C$1:$C$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'COUNT of Employee_ID'!$A$3:$A$9</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'COUNT of Employee_ID'!$C$3:$C$9</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'COUNT of Employee_ID'!$D$1:$D$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'COUNT of Employee_ID'!$A$3:$A$9</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'COUNT of Employee_ID'!$D$3:$D$9</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:overlap val="100"/>
+        <c:axId val="1819607708"/>
+        <c:axId val="1983233818"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1819607708"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1983233818"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1983233818"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1819607708"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>COUNTA of Name vs Location</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'COUNTA of Name vs Location'!$B$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
               <c:f>'COUNTA of Name vs Location'!$A$2:$A$7</c:f>
             </c:strRef>
           </c:cat>
@@ -3240,11 +2538,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1902748393"/>
-        <c:axId val="1604575293"/>
+        <c:axId val="1003011731"/>
+        <c:axId val="1998892792"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1902748393"/>
+        <c:axId val="1003011731"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3287,7 +2585,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="1">
+              <a:defRPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3296,15 +2594,24 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1604575293"/>
+        <c:crossAx val="1998892792"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1604575293"/>
+        <c:axId val="1998892792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:minorGridlines>
           <c:spPr>
             <a:ln>
@@ -3337,7 +2644,7 @@
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                   </a:rPr>
-                  <a:t>COUNT of Name</a:t>
+                  <a:t>COUNTA of Name</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -3356,7 +2663,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="1">
+              <a:defRPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3365,7 +2672,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1902748393"/>
+        <c:crossAx val="1003011731"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -3391,7 +2698,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
   <c:chart>
     <c:title>
@@ -3611,11 +2918,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="982082205"/>
-        <c:axId val="1203916328"/>
+        <c:axId val="416381173"/>
+        <c:axId val="1311705582"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="982082205"/>
+        <c:axId val="416381173"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3667,10 +2974,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1203916328"/>
+        <c:crossAx val="1311705582"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1203916328"/>
+        <c:axId val="1311705582"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3745,7 +3052,1066 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="982082205"/>
+        <c:crossAx val="416381173"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>AVERAGE of Salary of Job_Role</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Pivot Table 5'!$B$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+          </c:dPt>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pivot Table 5'!$A$2:$A$7</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pivot Table 5'!$B$2:$B$7</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:overlap val="100"/>
+        <c:axId val="1503782894"/>
+        <c:axId val="300922013"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1503782894"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Job_Role</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="300922013"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="300922013"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>AVERAGE of Salary</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1503782894"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Salary vs Experience_Years</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>hr_analytics_500_rows!$H$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln cmpd="sng">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>hr_analytics_500_rows!$G$2:$G$1000</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>hr_analytics_500_rows!$H$2:$H$1000</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1382667531"/>
+        <c:axId val="342290114"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1382667531"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Experience_Years</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="342290114"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="342290114"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Salary</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1382667531"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Department-wise Attrition Rate </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'COUNT of Employee_ID'!$B$1:$B$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'COUNT of Employee_ID'!$A$3:$A$9</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'COUNT of Employee_ID'!$B$3:$B$9</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'COUNT of Employee_ID'!$C$1:$C$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'COUNT of Employee_ID'!$A$3:$A$9</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'COUNT of Employee_ID'!$C$3:$C$9</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'COUNT of Employee_ID'!$D$1:$D$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'COUNT of Employee_ID'!$A$3:$A$9</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'COUNT of Employee_ID'!$D$3:$D$9</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:overlap val="100"/>
+        <c:axId val="1169908685"/>
+        <c:axId val="1135340857"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1169908685"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1135340857"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1135340857"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1" sz="1000">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1169908685"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="1">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Location-wise Employees</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'COUNTA of Name vs Location'!$B$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'COUNTA of Name vs Location'!$A$2:$A$7</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'COUNTA of Name vs Location'!$B$2:$B$7</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1234059994"/>
+        <c:axId val="1775806366"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1234059994"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Location</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1775806366"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1775806366"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>COUNT of Name</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1234059994"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -3962,14 +4328,18 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
     <xdr:graphicFrame>
@@ -3996,6 +4366,36 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5715000" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 2" title="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>809625</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -4004,7 +4404,7 @@
     <xdr:ext cx="5715000" cy="3533775"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 2" title="Chart"/>
+        <xdr:cNvPr id="3" name="Chart 3" title="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -4084,7 +4484,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -4092,36 +4492,6 @@
       <xdr:colOff>714375</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5715000" cy="3533775"/>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 3" title="Chart"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
     <xdr:graphicFrame>
@@ -4149,9 +4519,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
     <xdr:graphicFrame>
@@ -4178,15 +4548,45 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5715000" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 6" title="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
+      <xdr:colOff>228600</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3295650" cy="1790700"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12227847" name="Chart6" title="Chart">
+        <xdr:cNvPr id="12227847" name="Chart7" title="Chart">
           <a:extLst>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
               <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
@@ -4220,7 +4620,7 @@
     <xdr:ext cx="2809875" cy="1743075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1354639702" name="Chart7" title="Chart">
+        <xdr:cNvPr id="1354639702" name="Chart8" title="Chart">
           <a:extLst>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
               <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
@@ -4254,7 +4654,7 @@
     <xdr:ext cx="3962400" cy="2257425"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 8" title="Chart"/>
+        <xdr:cNvPr id="9" name="Chart 9" title="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -4272,14 +4672,14 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3362325" cy="2095500"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="9" name="Chart 9" title="Chart"/>
+        <xdr:cNvPr id="10" name="Chart 10" title="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -4304,7 +4704,7 @@
     <xdr:ext cx="3295650" cy="2162175"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="10" name="Chart 10" title="Chart"/>
+        <xdr:cNvPr id="11" name="Chart 11" title="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -4329,7 +4729,7 @@
     <xdr:ext cx="3790950" cy="1790700"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="11" name="Chart 11" title="Chart"/>
+        <xdr:cNvPr id="12" name="Chart 12" title="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -4354,7 +4754,7 @@
     <xdr:ext cx="3419475" cy="2181225"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="12" name="Chart 12" title="Chart"/>
+        <xdr:cNvPr id="13" name="Chart 13" title="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -4372,14 +4772,14 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>76200</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4029075" cy="1866900"/>
+    <xdr:ext cx="3886200" cy="1895475"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="13" name="Chart 13" title="Chart"/>
+        <xdr:cNvPr id="14" name="Chart 14" title="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -4645,7 +5045,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -4657,7 +5057,7 @@
     <xdr:ext cx="5715000" cy="3533775"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="14" name="Chart 14" title="Chart"/>
+        <xdr:cNvPr id="15" name="Chart 15" title="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -8144,6 +8544,1775 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot Table 17" cacheId="0" dataCaption="" rowGrandTotals="0" compact="0" compactData="0">
+  <location ref="A1:B7" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields>
+    <pivotField name="Employee_ID" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item x="368"/>
+        <item x="369"/>
+        <item x="370"/>
+        <item x="371"/>
+        <item x="372"/>
+        <item x="373"/>
+        <item x="374"/>
+        <item x="375"/>
+        <item x="376"/>
+        <item x="377"/>
+        <item x="378"/>
+        <item x="379"/>
+        <item x="380"/>
+        <item x="381"/>
+        <item x="382"/>
+        <item x="383"/>
+        <item x="384"/>
+        <item x="385"/>
+        <item x="386"/>
+        <item x="387"/>
+        <item x="388"/>
+        <item x="389"/>
+        <item x="390"/>
+        <item x="391"/>
+        <item x="392"/>
+        <item x="393"/>
+        <item x="394"/>
+        <item x="395"/>
+        <item x="396"/>
+        <item x="397"/>
+        <item x="398"/>
+        <item x="399"/>
+        <item x="400"/>
+        <item x="401"/>
+        <item x="402"/>
+        <item x="403"/>
+        <item x="404"/>
+        <item x="405"/>
+        <item x="406"/>
+        <item x="407"/>
+        <item x="408"/>
+        <item x="409"/>
+        <item x="410"/>
+        <item x="411"/>
+        <item x="412"/>
+        <item x="413"/>
+        <item x="414"/>
+        <item x="415"/>
+        <item x="416"/>
+        <item x="417"/>
+        <item x="418"/>
+        <item x="419"/>
+        <item x="420"/>
+        <item x="421"/>
+        <item x="422"/>
+        <item x="423"/>
+        <item x="424"/>
+        <item x="425"/>
+        <item x="426"/>
+        <item x="427"/>
+        <item x="428"/>
+        <item x="429"/>
+        <item x="430"/>
+        <item x="431"/>
+        <item x="432"/>
+        <item x="433"/>
+        <item x="434"/>
+        <item x="435"/>
+        <item x="436"/>
+        <item x="437"/>
+        <item x="438"/>
+        <item x="439"/>
+        <item x="440"/>
+        <item x="441"/>
+        <item x="442"/>
+        <item x="443"/>
+        <item x="444"/>
+        <item x="445"/>
+        <item x="446"/>
+        <item x="447"/>
+        <item x="448"/>
+        <item x="449"/>
+        <item x="450"/>
+        <item x="451"/>
+        <item x="452"/>
+        <item x="453"/>
+        <item x="454"/>
+        <item x="455"/>
+        <item x="456"/>
+        <item x="457"/>
+        <item x="458"/>
+        <item x="459"/>
+        <item x="460"/>
+        <item x="461"/>
+        <item x="462"/>
+        <item x="463"/>
+        <item x="464"/>
+        <item x="465"/>
+        <item x="466"/>
+        <item x="467"/>
+        <item x="468"/>
+        <item x="469"/>
+        <item x="470"/>
+        <item x="471"/>
+        <item x="472"/>
+        <item x="473"/>
+        <item x="474"/>
+        <item x="475"/>
+        <item x="476"/>
+        <item x="477"/>
+        <item x="478"/>
+        <item x="479"/>
+        <item x="480"/>
+        <item x="481"/>
+        <item x="482"/>
+        <item x="483"/>
+        <item x="484"/>
+        <item x="485"/>
+        <item x="486"/>
+        <item x="487"/>
+        <item x="488"/>
+        <item x="489"/>
+        <item x="490"/>
+        <item x="491"/>
+        <item x="492"/>
+        <item x="493"/>
+        <item x="494"/>
+        <item x="495"/>
+        <item x="496"/>
+        <item x="497"/>
+        <item x="498"/>
+        <item x="499"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Name" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Age" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Gender" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Department" axis="axisRow" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
+      <items>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Job_Role" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Experience_Years" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Salary" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item x="368"/>
+        <item x="369"/>
+        <item x="370"/>
+        <item x="371"/>
+        <item x="372"/>
+        <item x="373"/>
+        <item x="374"/>
+        <item x="375"/>
+        <item x="376"/>
+        <item x="377"/>
+        <item x="378"/>
+        <item x="379"/>
+        <item x="380"/>
+        <item x="381"/>
+        <item x="382"/>
+        <item x="383"/>
+        <item x="384"/>
+        <item x="385"/>
+        <item x="386"/>
+        <item x="387"/>
+        <item x="388"/>
+        <item x="389"/>
+        <item x="390"/>
+        <item x="391"/>
+        <item x="392"/>
+        <item x="393"/>
+        <item x="394"/>
+        <item x="395"/>
+        <item x="396"/>
+        <item x="397"/>
+        <item x="398"/>
+        <item x="399"/>
+        <item x="400"/>
+        <item x="401"/>
+        <item x="402"/>
+        <item x="403"/>
+        <item x="404"/>
+        <item x="405"/>
+        <item x="406"/>
+        <item x="407"/>
+        <item x="408"/>
+        <item x="409"/>
+        <item x="410"/>
+        <item x="411"/>
+        <item x="412"/>
+        <item x="413"/>
+        <item x="414"/>
+        <item x="415"/>
+        <item x="416"/>
+        <item x="417"/>
+        <item x="418"/>
+        <item x="419"/>
+        <item x="420"/>
+        <item x="421"/>
+        <item x="422"/>
+        <item x="423"/>
+        <item x="424"/>
+        <item x="425"/>
+        <item x="426"/>
+        <item x="427"/>
+        <item x="428"/>
+        <item x="429"/>
+        <item x="430"/>
+        <item x="431"/>
+        <item x="432"/>
+        <item x="433"/>
+        <item x="434"/>
+        <item x="435"/>
+        <item x="436"/>
+        <item x="437"/>
+        <item x="438"/>
+        <item x="439"/>
+        <item x="440"/>
+        <item x="441"/>
+        <item x="442"/>
+        <item x="443"/>
+        <item x="444"/>
+        <item x="445"/>
+        <item x="446"/>
+        <item x="447"/>
+        <item x="448"/>
+        <item x="449"/>
+        <item x="450"/>
+        <item x="451"/>
+        <item x="452"/>
+        <item x="453"/>
+        <item x="454"/>
+        <item x="455"/>
+        <item x="456"/>
+        <item x="457"/>
+        <item x="458"/>
+        <item x="459"/>
+        <item x="460"/>
+        <item x="461"/>
+        <item x="462"/>
+        <item x="463"/>
+        <item x="464"/>
+        <item x="465"/>
+        <item x="466"/>
+        <item x="467"/>
+        <item x="468"/>
+        <item x="469"/>
+        <item x="470"/>
+        <item x="471"/>
+        <item x="472"/>
+        <item x="473"/>
+        <item x="474"/>
+        <item x="475"/>
+        <item x="476"/>
+        <item x="477"/>
+        <item x="478"/>
+        <item x="479"/>
+        <item x="480"/>
+        <item x="481"/>
+        <item x="482"/>
+        <item x="483"/>
+        <item x="484"/>
+        <item x="485"/>
+        <item x="486"/>
+        <item x="487"/>
+        <item x="488"/>
+        <item x="489"/>
+        <item x="490"/>
+        <item x="491"/>
+        <item x="492"/>
+        <item x="493"/>
+        <item x="494"/>
+        <item x="495"/>
+        <item x="496"/>
+        <item x="497"/>
+        <item x="498"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Location" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Education" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Attrition" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Performance_Rating" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Joining_Date" compact="0" numFmtId="164" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item x="368"/>
+        <item x="369"/>
+        <item x="370"/>
+        <item x="371"/>
+        <item x="372"/>
+        <item x="373"/>
+        <item x="374"/>
+        <item x="375"/>
+        <item x="376"/>
+        <item x="377"/>
+        <item x="378"/>
+        <item x="379"/>
+        <item x="380"/>
+        <item x="381"/>
+        <item x="382"/>
+        <item x="383"/>
+        <item x="384"/>
+        <item x="385"/>
+        <item x="386"/>
+        <item x="387"/>
+        <item x="388"/>
+        <item x="389"/>
+        <item x="390"/>
+        <item x="391"/>
+        <item x="392"/>
+        <item x="393"/>
+        <item x="394"/>
+        <item x="395"/>
+        <item x="396"/>
+        <item x="397"/>
+        <item x="398"/>
+        <item x="399"/>
+        <item x="400"/>
+        <item x="401"/>
+        <item x="402"/>
+        <item x="403"/>
+        <item x="404"/>
+        <item x="405"/>
+        <item x="406"/>
+        <item x="407"/>
+        <item x="408"/>
+        <item x="409"/>
+        <item x="410"/>
+        <item x="411"/>
+        <item x="412"/>
+        <item x="413"/>
+        <item x="414"/>
+        <item x="415"/>
+        <item x="416"/>
+        <item x="417"/>
+        <item x="418"/>
+        <item x="419"/>
+        <item x="420"/>
+        <item x="421"/>
+        <item x="422"/>
+        <item x="423"/>
+        <item x="424"/>
+        <item x="425"/>
+        <item x="426"/>
+        <item x="427"/>
+        <item x="428"/>
+        <item x="429"/>
+        <item x="430"/>
+        <item x="431"/>
+        <item x="432"/>
+        <item x="433"/>
+        <item x="434"/>
+        <item x="435"/>
+        <item x="436"/>
+        <item x="437"/>
+        <item x="438"/>
+        <item x="439"/>
+        <item x="440"/>
+        <item x="441"/>
+        <item x="442"/>
+        <item x="443"/>
+        <item x="444"/>
+        <item x="445"/>
+        <item x="446"/>
+        <item x="447"/>
+        <item x="448"/>
+        <item x="449"/>
+        <item x="450"/>
+        <item x="451"/>
+        <item x="452"/>
+        <item x="453"/>
+        <item x="454"/>
+        <item x="455"/>
+        <item x="456"/>
+        <item x="457"/>
+        <item x="458"/>
+        <item x="459"/>
+        <item x="460"/>
+        <item x="461"/>
+        <item x="462"/>
+        <item x="463"/>
+        <item x="464"/>
+        <item x="465"/>
+        <item x="466"/>
+        <item x="467"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Month" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Year" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields>
+    <field x="4"/>
+  </rowFields>
+  <dataFields>
+    <dataField name="COUNTA of Department" fld="4" subtotal="count" baseField="0"/>
+  </dataFields>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="COUNT of Employee_ID" cacheId="0" dataCaption="" rowGrandTotals="0" colGrandTotals="0" compact="0" compactData="0">
   <location ref="A1:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields>
@@ -9915,7 +12084,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="COUNTA of Name vs Location" cacheId="0" dataCaption="" compact="0" compactData="0">
   <location ref="A1:B8" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
   <pivotFields>
@@ -11684,7 +13853,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Year Hiring Trend" cacheId="0" dataCaption="" compact="0" compactData="0">
   <location ref="A1:H19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields>
@@ -13456,7 +15625,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot Table 5" cacheId="1" dataCaption="" compact="0" compactData="0">
   <location ref="A1:B7" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
   <pivotFields>
@@ -15187,7 +17356,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot Table 2" cacheId="1" dataCaption="" compact="0" compactData="0">
   <location ref="A1:B8" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
   <pivotFields>
@@ -17005,6 +19174,27 @@
 </table>
 </file>
 
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M79" displayName="Table_2" name="Table_2" id="2">
+  <tableColumns count="13">
+    <tableColumn name="Employee_ID" id="1"/>
+    <tableColumn name="Name" id="2"/>
+    <tableColumn name="Age" id="3"/>
+    <tableColumn name="Gender" id="4"/>
+    <tableColumn name="Department" id="5"/>
+    <tableColumn name="Job_Role" id="6"/>
+    <tableColumn name="Experience_Years" id="7"/>
+    <tableColumn name="Salary" id="8"/>
+    <tableColumn name="Location" id="9"/>
+    <tableColumn name="Education" id="10"/>
+    <tableColumn name="Attrition" id="11"/>
+    <tableColumn name="Performance_Rating" id="12"/>
+    <tableColumn name="Joining_Date" id="13"/>
+  </tableColumns>
+  <tableStyleInfo name="Detail2-Marketing-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
@@ -43255,13 +45445,13 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{3B717D27-9F4F-4753-8CC6-37024164C384}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{EB8B8BF7-1C38-44E1-877B-F903761F8CA0}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$O$501"/>
     </customSheetView>
-    <customSheetView guid="{3B717D27-9F4F-4753-8CC6-37024164C384}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{EB8B8BF7-1C38-44E1-877B-F903761F8CA0}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$O$501"/>
     </customSheetView>
-    <customSheetView guid="{3B717D27-9F4F-4753-8CC6-37024164C384}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{EB8B8BF7-1C38-44E1-877B-F903761F8CA0}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$O$501"/>
     </customSheetView>
   </customSheetViews>
@@ -43279,7 +45469,3280 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="14">
+        <v>40.0</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="H2" s="14">
+        <v>36968.0</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M2" s="15">
+        <v>44036.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="14">
+        <v>60.0</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="14">
+        <v>11.0</v>
+      </c>
+      <c r="H3" s="14">
+        <v>36249.0</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M3" s="15">
+        <v>42104.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="14">
+        <v>56.0</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="14">
+        <v>9.0</v>
+      </c>
+      <c r="H4" s="14">
+        <v>60448.0</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M4" s="15">
+        <v>42806.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="14">
+        <v>42.0</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="H5" s="14">
+        <v>42104.0</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M5" s="15">
+        <v>42504.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13">
+        <v>13.0</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="14">
+        <v>24.0</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="H6" s="14">
+        <v>109052.0</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M6" s="15">
+        <v>44959.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13">
+        <v>25.0</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="14">
+        <v>28.0</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="14">
+        <v>8.0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>45024.0</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M7" s="15">
+        <v>43205.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13">
+        <v>29.0</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="14">
+        <v>56.0</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>88644.0</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M8" s="15">
+        <v>44239.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13">
+        <v>55.0</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="14">
+        <v>26.0</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="14">
+        <v>15.0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>78281.0</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M9" s="15">
+        <v>40797.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13">
+        <v>75.0</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="14">
+        <v>44.0</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>114042.0</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M10" s="15">
+        <v>43581.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13">
+        <v>77.0</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="14">
+        <v>56.0</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="14">
+        <v>8.0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>109265.0</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M11" s="15">
+        <v>43235.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13">
+        <v>78.0</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="14">
+        <v>43.0</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>52697.0</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M12" s="15">
+        <v>44180.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13">
+        <v>90.0</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="14">
+        <v>53.0</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>34667.0</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M13" s="15">
+        <v>42716.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13">
+        <v>92.0</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="14">
+        <v>38.0</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>54627.0</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M14" s="15">
+        <v>42693.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13">
+        <v>97.0</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="14">
+        <v>24.0</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>99161.0</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M15" s="15">
+        <v>44045.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13">
+        <v>98.0</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="14">
+        <v>43.0</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="14">
+        <v>14.0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>105902.0</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M16" s="15">
+        <v>40909.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13">
+        <v>99.0</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60.0</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="14">
+        <v>13.0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>64348.0</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M17" s="15">
+        <v>41387.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13">
+        <v>102.0</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="14">
+        <v>23.0</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="14">
+        <v>11.0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>57369.0</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M18" s="15">
+        <v>42104.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13">
+        <v>108.0</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="14">
+        <v>42.0</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="14">
+        <v>15.0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>115031.0</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M19" s="15">
+        <v>40577.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13">
+        <v>109.0</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="14">
+        <v>41.0</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="14">
+        <v>11.0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>39509.0</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M20" s="15">
+        <v>42348.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13">
+        <v>117.0</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="14">
+        <v>47.0</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" s="14">
+        <v>9.0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>97227.0</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M21" s="15">
+        <v>42908.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13">
+        <v>121.0</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="14">
+        <v>46.0</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>62410.0</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M22" s="15">
+        <v>45309.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13">
+        <v>135.0</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="14">
+        <v>58.0</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>102701.0</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M23" s="15">
+        <v>43513.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13">
+        <v>154.0</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="14">
+        <v>60.0</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="14">
+        <v>14.0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>112252.0</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M24" s="15">
+        <v>40986.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13">
+        <v>173.0</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="14">
+        <v>60.0</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>46642.0</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M25" s="15">
+        <v>43734.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13">
+        <v>179.0</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="14">
+        <v>22.0</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="14">
+        <v>15.0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>89952.0</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M26" s="15">
+        <v>40691.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13">
+        <v>180.0</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="14">
+        <v>22.0</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" s="14">
+        <v>9.0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>76554.0</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M27" s="15">
+        <v>42965.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13">
+        <v>184.0</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="14">
+        <v>34.0</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>32469.0</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M28" s="15">
+        <v>44141.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13">
+        <v>188.0</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="14">
+        <v>48.0</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>72000.0</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M29" s="15">
+        <v>44840.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13">
+        <v>197.0</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="14">
+        <v>23.0</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>39919.0</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M30" s="15">
+        <v>44838.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13">
+        <v>199.0</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="14">
+        <v>46.0</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" s="14">
+        <v>13.0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>114682.0</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M31" s="15">
+        <v>41557.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13">
+        <v>201.0</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" s="14">
+        <v>47.0</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" s="14">
+        <v>11.0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>89516.0</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M32" s="15">
+        <v>42279.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13">
+        <v>203.0</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="14">
+        <v>46.0</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>20445.0</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M33" s="15">
+        <v>45181.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13">
+        <v>206.0</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="14">
+        <v>32.0</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G34" s="14">
+        <v>15.0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>68454.0</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L34" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M34" s="15">
+        <v>40629.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13">
+        <v>210.0</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="14">
+        <v>59.0</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>59022.0</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M35" s="15">
+        <v>45839.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13">
+        <v>211.0</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="14">
+        <v>22.0</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" s="14">
+        <v>11.0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>82994.0</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M36" s="15">
+        <v>42131.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13">
+        <v>213.0</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="14">
+        <v>23.0</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G37" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>86365.0</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M37" s="15">
+        <v>45694.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13">
+        <v>219.0</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="14">
+        <v>50.0</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>34831.0</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L38" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M38" s="15">
+        <v>43634.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13">
+        <v>222.0</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="14">
+        <v>48.0</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G39" s="14">
+        <v>14.0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>77860.0</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M39" s="15">
+        <v>41262.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13">
+        <v>226.0</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="14">
+        <v>51.0</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="14">
+        <v>13.0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>109132.0</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M40" s="15">
+        <v>41449.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13">
+        <v>229.0</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="14">
+        <v>54.0</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>52161.0</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M41" s="15">
+        <v>43482.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13">
+        <v>246.0</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="14">
+        <v>49.0</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>75732.0</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M42" s="15">
+        <v>42498.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13">
+        <v>250.0</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="14">
+        <v>46.0</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>33939.0</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M43" s="15">
+        <v>42477.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13">
+        <v>258.0</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="14">
+        <v>27.0</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G44" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>37938.0</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J44" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M44" s="15">
+        <v>44342.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13">
+        <v>260.0</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" s="14">
+        <v>42.0</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>66740.0</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J45" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M45" s="15">
+        <v>44708.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13">
+        <v>290.0</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" s="14">
+        <v>43.0</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G46" s="14">
+        <v>8.0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>27409.0</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M46" s="15">
+        <v>43106.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13">
+        <v>292.0</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="14">
+        <v>53.0</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>21763.0</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M47" s="15">
+        <v>46271.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13">
+        <v>312.0</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="14">
+        <v>27.0</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G48" s="14">
+        <v>9.0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>98774.0</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M48" s="15">
+        <v>42774.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13">
+        <v>318.0</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="14">
+        <v>60.0</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G49" s="14">
+        <v>11.0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>108861.0</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J49" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M49" s="15">
+        <v>42328.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13">
+        <v>320.0</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" s="14">
+        <v>32.0</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>105813.0</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J50" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L50" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M50" s="15">
+        <v>43791.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13">
+        <v>321.0</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" s="14">
+        <v>47.0</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G51" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>107617.0</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J51" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M51" s="15">
+        <v>45529.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13">
+        <v>323.0</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="14">
+        <v>50.0</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="14">
+        <v>12.0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>54432.0</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J52" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L52" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M52" s="15">
+        <v>41832.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13">
+        <v>326.0</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C53" s="14">
+        <v>44.0</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G53" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>108939.0</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J53" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M53" s="15">
+        <v>45861.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13">
+        <v>344.0</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="14">
+        <v>24.0</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" s="14">
+        <v>15.0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>64679.0</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J54" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M54" s="15">
+        <v>40886.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13">
+        <v>348.0</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C55" s="14">
+        <v>52.0</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>86117.0</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J55" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K55" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L55" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M55" s="15">
+        <v>45262.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13">
+        <v>368.0</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C56" s="14">
+        <v>43.0</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" s="14">
+        <v>12.0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>35956.0</v>
+      </c>
+      <c r="I56" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J56" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L56" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M56" s="15">
+        <v>41787.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13">
+        <v>373.0</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C57" s="14">
+        <v>27.0</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G57" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>57379.0</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M57" s="15">
+        <v>45824.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13">
+        <v>379.0</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" s="14">
+        <v>51.0</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G58" s="14">
+        <v>8.0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>96997.0</v>
+      </c>
+      <c r="I58" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J58" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L58" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M58" s="15">
+        <v>43214.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13">
+        <v>385.0</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59" s="14">
+        <v>60.0</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G59" s="14">
+        <v>12.0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>38129.0</v>
+      </c>
+      <c r="I59" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J59" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K59" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L59" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M59" s="15">
+        <v>41981.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13">
+        <v>392.0</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" s="14">
+        <v>55.0</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G60" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>35557.0</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J60" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K60" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L60" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M60" s="15">
+        <v>42482.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13">
+        <v>397.0</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C61" s="14">
+        <v>29.0</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G61" s="14">
+        <v>9.0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>104600.0</v>
+      </c>
+      <c r="I61" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J61" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K61" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M61" s="15">
+        <v>42790.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13">
+        <v>400.0</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" s="14">
+        <v>35.0</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G62" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>20648.0</v>
+      </c>
+      <c r="I62" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J62" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K62" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M62" s="15">
+        <v>42546.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13">
+        <v>407.0</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C63" s="14">
+        <v>48.0</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G63" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>70483.0</v>
+      </c>
+      <c r="I63" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J63" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M63" s="15">
+        <v>43901.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13">
+        <v>411.0</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="14">
+        <v>58.0</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" s="14">
+        <v>15.0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>86969.0</v>
+      </c>
+      <c r="I64" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J64" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K64" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L64" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M64" s="15">
+        <v>40669.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13">
+        <v>419.0</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C65" s="14">
+        <v>36.0</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G65" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>51167.0</v>
+      </c>
+      <c r="I65" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J65" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K65" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M65" s="15">
+        <v>44371.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13">
+        <v>420.0</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" s="14">
+        <v>43.0</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>74368.0</v>
+      </c>
+      <c r="I66" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J66" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K66" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L66" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M66" s="15">
+        <v>45275.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13">
+        <v>428.0</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C67" s="14">
+        <v>60.0</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G67" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>95271.0</v>
+      </c>
+      <c r="I67" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J67" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K67" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M67" s="15">
+        <v>42708.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13">
+        <v>436.0</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C68" s="14">
+        <v>55.0</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G68" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>64378.0</v>
+      </c>
+      <c r="I68" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J68" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K68" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L68" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M68" s="15">
+        <v>44077.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13">
+        <v>442.0</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C69" s="14">
+        <v>24.0</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>40621.0</v>
+      </c>
+      <c r="I69" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K69" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L69" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M69" s="15">
+        <v>46005.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13">
+        <v>443.0</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="14">
+        <v>40.0</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G70" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>82148.0</v>
+      </c>
+      <c r="I70" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J70" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K70" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L70" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M70" s="15">
+        <v>44677.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13">
+        <v>444.0</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71" s="14">
+        <v>58.0</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G71" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>30036.0</v>
+      </c>
+      <c r="I71" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J71" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K71" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L71" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M71" s="15">
+        <v>43658.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13">
+        <v>445.0</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" s="14">
+        <v>52.0</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G72" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>23639.0</v>
+      </c>
+      <c r="I72" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J72" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L72" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M72" s="15">
+        <v>43923.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13">
+        <v>446.0</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" s="14">
+        <v>54.0</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G73" s="14">
+        <v>14.0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>81382.0</v>
+      </c>
+      <c r="I73" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J73" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K73" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M73" s="15">
+        <v>41236.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13">
+        <v>460.0</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" s="14">
+        <v>48.0</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G74" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="H74" s="14">
+        <v>88640.0</v>
+      </c>
+      <c r="I74" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J74" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L74" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="M74" s="15">
+        <v>43595.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13">
+        <v>468.0</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C75" s="14">
+        <v>55.0</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E75" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G75" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="H75" s="14">
+        <v>93401.0</v>
+      </c>
+      <c r="I75" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J75" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K75" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M75" s="15">
+        <v>44389.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13">
+        <v>472.0</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C76" s="14">
+        <v>34.0</v>
+      </c>
+      <c r="D76" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G76" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="H76" s="14">
+        <v>115289.0</v>
+      </c>
+      <c r="I76" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J76" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K76" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L76" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="M76" s="15">
+        <v>44729.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13">
+        <v>474.0</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" s="14">
+        <v>48.0</v>
+      </c>
+      <c r="D77" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="H77" s="14">
+        <v>78228.0</v>
+      </c>
+      <c r="I77" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J77" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K77" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L77" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="M77" s="15">
+        <v>45422.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13">
+        <v>489.0</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C78" s="14">
+        <v>42.0</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E78" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G78" s="14">
+        <v>15.0</v>
+      </c>
+      <c r="H78" s="14">
+        <v>57435.0</v>
+      </c>
+      <c r="I78" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J78" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K78" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L78" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="M78" s="15">
+        <v>40637.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13">
+        <v>500.0</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C79" s="14">
+        <v>28.0</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G79" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="H79" s="14">
+        <v>51382.0</v>
+      </c>
+      <c r="I79" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J79" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K79" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L79" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M79" s="15">
+        <v>45666.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+  </sheetData>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -49377,7 +54840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -49407,7 +54870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -49432,7 +54895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -49463,7 +54926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -49493,7 +54956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -49502,7 +54965,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3">
@@ -50353,7 +55816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
